--- a/docs/downloads/07/tbl_parcelles_stats_marovoay_tous.xlsx
+++ b/docs/downloads/07/tbl_parcelles_stats_marovoay_tous.xlsx
@@ -394,7 +394,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2">
@@ -419,7 +419,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B3">
@@ -444,7 +444,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B4">
@@ -469,7 +469,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B5">
@@ -494,7 +494,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B6">
